--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486882_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486882_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>J. PARRA BAEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9584</v>
+        <v>6.6731</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9892</v>
+        <v>3.9751</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9692</v>
+        <v>2.698</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2814</v>
+        <v>3.1857</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9205</v>
+        <v>2.6018</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6391</v>
+        <v>0.5839</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8094</v>
+        <v>3.5138</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6385</v>
+        <v>2.5145</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1709</v>
+        <v>0.9993</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5281</v>
+        <v>-0.3281</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2819</v>
+        <v>0.0873</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.4154</v>
       </c>
       <c r="P2" t="n">
-        <v>1.2321</v>
+        <v>2.6694</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2855</v>
+        <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2582</v>
+        <v>0.2286</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0464</v>
+        <v>-0.128</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2118</v>
+        <v>0.3566</v>
       </c>
       <c r="V2" t="n">
-        <v>3.1868</v>
+        <v>0.5893</v>
       </c>
       <c r="W2" t="n">
-        <v>3.1868</v>
+        <v>0.5893</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PARRA BAEZ</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0315</v>
+        <v>6.0287</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4521</v>
+        <v>2.7413</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5794</v>
+        <v>3.2874</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1857</v>
+        <v>1.2814</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6018</v>
+        <v>1.9205</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5839</v>
+        <v>-0.6391</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5138</v>
+        <v>1.8094</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5145</v>
+        <v>1.6385</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9993</v>
+        <v>0.1709</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3281</v>
+        <v>-0.5281</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0873</v>
+        <v>0.2819</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4154</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6694</v>
+        <v>1.2321</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6694</v>
+        <v>3.2855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.413</v>
+        <v>0.3284</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.651</v>
+        <v>-0.2016</v>
       </c>
       <c r="U3" t="n">
-        <v>0.238</v>
+        <v>0.53</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5893</v>
+        <v>3.1868</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5893</v>
+        <v>3.1868</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3657</v>
+        <v>4.4909</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7528</v>
+        <v>1.8187</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6129</v>
+        <v>2.6721</v>
       </c>
       <c r="G4" t="n">
         <v>4.1286</v>
@@ -766,13 +766,13 @@
         <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4425</v>
+        <v>0.5676</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1704</v>
+        <v>0.2362</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2721</v>
+        <v>0.3314</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ALVAREZ PUERTAS</t>
+          <t>P. ARRIBAS GOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.878</v>
+        <v>2.52</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3576</v>
+        <v>1.5308</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5203</v>
+        <v>0.9892</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2323</v>
+        <v>0.9102</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2982</v>
+        <v>-0.7527</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0659</v>
+        <v>1.6629</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1219</v>
+        <v>1.3333</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4774</v>
+        <v>0.1363</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6445</v>
+        <v>1.197</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3542</v>
+        <v>-0.4231</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7756</v>
+        <v>-0.889</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5786</v>
+        <v>0.4659</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8515</v>
+        <v>0.2073</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2357</v>
+        <v>0.1975</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6158</v>
+        <v>0.0098</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5893</v>
+        <v>-0.2402</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5893</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>M. ALVAREZ PUERTAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7965</v>
+        <v>2.1161</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3789</v>
+        <v>1.6254</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4176</v>
+        <v>0.4907</v>
       </c>
       <c r="G6" t="n">
-        <v>0.904</v>
+        <v>-0.2323</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0355</v>
+        <v>-0.2982</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9395</v>
+        <v>0.0659</v>
       </c>
       <c r="J6" t="n">
-        <v>0.206</v>
+        <v>1.1219</v>
       </c>
       <c r="K6" t="n">
-        <v>0.127</v>
+        <v>0.4774</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0789</v>
+        <v>0.6445</v>
       </c>
       <c r="M6" t="n">
-        <v>0.698</v>
+        <v>-1.3542</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1626</v>
+        <v>-0.7756</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8606</v>
+        <v>-0.5786</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2053</v>
+        <v>1.8481</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1451</v>
+        <v>1.0896</v>
       </c>
       <c r="T6" t="n">
-        <v>2.828</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3171</v>
+        <v>0.5861</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0472</v>
+        <v>-0.5893</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3716</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4189</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ARRIBAS GOMEZ</t>
+          <t>A. AKINWOLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3808</v>
+        <v>1.8664</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5695</v>
+        <v>0.2557</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8113</v>
+        <v>1.6107</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9102</v>
+        <v>2.3468</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7527</v>
+        <v>2.91</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6629</v>
+        <v>-0.5632</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3333</v>
+        <v>3.0879</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1363</v>
+        <v>3.3515</v>
       </c>
       <c r="L7" t="n">
-        <v>1.197</v>
+        <v>-0.2636</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4231</v>
+        <v>-0.7411</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.889</v>
+        <v>-0.4415</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4659</v>
+        <v>-0.2996</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6427</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q7" t="n">
+        <v>-3.0801</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.0534</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.2402</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.2402</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.6427</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.0682</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.2362</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.1681</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.2402</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.2402</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. ORTIZ TORRES</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4767</v>
+        <v>1.4957</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1694</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3073</v>
+        <v>2.4297</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7842</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>2.021</v>
+        <v>2.3877</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2368</v>
+        <v>-1.5051</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5521</v>
+        <v>1.1264</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9076</v>
+        <v>1.7977</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6445</v>
+        <v>-0.6713</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7679</v>
+        <v>-0.2438</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1134</v>
+        <v>0.59</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8813</v>
+        <v>-0.8338</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2053</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0534</v>
+        <v>-4.1068</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8481</v>
+        <v>2.4641</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1022</v>
+        <v>0.3565</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3294</v>
+        <v>0.1471</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2271</v>
+        <v>0.2094</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.8993</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8993</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. AKINWOLE</t>
+          <t>E. ORTIZ TORRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8312</v>
+        <v>1.4627</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5424</v>
+        <v>0.274</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3736</v>
+        <v>1.1887</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3468</v>
+        <v>1.7842</v>
       </c>
       <c r="H9" t="n">
-        <v>2.91</v>
+        <v>2.021</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5632</v>
+        <v>-0.2368</v>
       </c>
       <c r="J9" t="n">
-        <v>3.0879</v>
+        <v>2.5521</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3515</v>
+        <v>1.9076</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2636</v>
+        <v>0.6445</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7411</v>
+        <v>-0.7679</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4415</v>
+        <v>0.1134</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2996</v>
+        <v>-0.8813</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7291</v>
+        <v>-0.1162</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7905</v>
+        <v>-0.2248</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0613</v>
+        <v>0.1086</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7503</v>
+        <v>1.2341</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.798</v>
+        <v>0.8758</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5483</v>
+        <v>0.3583</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.904</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3877</v>
+        <v>-0.0355</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5051</v>
+        <v>0.9395</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1264</v>
+        <v>0.206</v>
       </c>
       <c r="K10" t="n">
-        <v>1.7977</v>
+        <v>0.127</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6713</v>
+        <v>0.0789</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2438</v>
+        <v>0.698</v>
       </c>
       <c r="N10" t="n">
-        <v>0.59</v>
+        <v>-0.1626</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8338</v>
+        <v>0.8606</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6427</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4641</v>
+        <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3889</v>
+        <v>1.5827</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7169</v>
+        <v>1.3249</v>
       </c>
       <c r="U10" t="n">
-        <v>0.328</v>
+        <v>0.2578</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8993</v>
+        <v>-1.0472</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8993</v>
+        <v>0.3716</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.239</v>
+        <v>1.0947</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1115</v>
+        <v>0.7004</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1275</v>
+        <v>0.3943</v>
       </c>
       <c r="G11" t="n">
         <v>2.8275</v>
@@ -1312,13 +1312,13 @@
         <v>1.4374</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1859</v>
+        <v>-0.3303</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8486</v>
+        <v>-0.2597</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3373</v>
+        <v>-0.0706</v>
       </c>
       <c r="V11" t="n">
         <v>0.2402</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7377</v>
+        <v>-0.9396</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1585</v>
+        <v>-0.3604</v>
       </c>
       <c r="F12" t="n">
         <v>-0.5792</v>
@@ -1390,10 +1390,10 @@
         <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4261</v>
+        <v>0.372</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5928</v>
+        <v>0.2052</v>
       </c>
       <c r="U12" t="n">
         <v>0.1667</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6323</v>
+        <v>-3.0458</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0675</v>
+        <v>-0.4942</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6998</v>
+        <v>-2.5516</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5016</v>
@@ -1468,13 +1468,13 @@
         <v>0.616</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.464</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9413</v>
+        <v>0.3796</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0638</v>
+        <v>0.0844</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5975</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>24.3381</v>
+        <v>24.997</v>
       </c>
       <c r="E14" t="n">
-        <v>11.3496</v>
+        <v>12.0086</v>
       </c>
       <c r="F14" t="n">
-        <v>12.9884</v>
+        <v>12.9883</v>
       </c>
       <c r="G14" t="n">
         <v>16.7065</v>
@@ -1531,10 +1531,10 @@
         <v>-3.6487</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6524000000000001</v>
+        <v>-0.6523999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.9965</v>
+        <v>-2.996500000000001</v>
       </c>
       <c r="P14" t="n">
         <v>3.080299999999999</v>
@@ -1546,10 +1546,10 @@
         <v>21.5609</v>
       </c>
       <c r="S14" t="n">
-        <v>4.397799999999998</v>
+        <v>5.0563</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5288</v>
+        <v>2.1875</v>
       </c>
       <c r="U14" t="n">
         <v>2.8687</v>
@@ -1558,7 +1558,7 @@
         <v>0.1538999999999993</v>
       </c>
       <c r="W14" t="n">
-        <v>7.9463</v>
+        <v>7.946299999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-7.792400000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7611</v>
+        <v>1.8953</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7953</v>
+        <v>1.8999</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0342</v>
+        <v>-0.0046</v>
       </c>
       <c r="G15" t="n">
         <v>1.9466</v>
@@ -1624,13 +1624,13 @@
         <v>0.8214</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0198</v>
+        <v>0.154</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1899</v>
+        <v>-0.0853</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2097</v>
+        <v>0.2393</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4334</v>
+        <v>1.3234</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3958</v>
+        <v>1.7096</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0376</v>
+        <v>-0.3861</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3619</v>
@@ -1702,13 +1702,13 @@
         <v>2.4641</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9061</v>
+        <v>-1.016</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9494</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0433</v>
+        <v>-0.3804</v>
       </c>
       <c r="V16" t="n">
         <v>4.3174</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.5481</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3531</v>
+        <v>0.6209</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4357</v>
+        <v>-1.1689</v>
       </c>
       <c r="G17" t="n">
         <v>0.7934</v>
@@ -1780,13 +1780,13 @@
         <v>2.2588</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6708</v>
+        <v>-1.1362</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4802</v>
+        <v>-0.252</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.151</v>
+        <v>-0.8842</v>
       </c>
       <c r="V17" t="n">
         <v>-0.4107</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1293</v>
+        <v>-0.5715</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0292</v>
+        <v>0.4476</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1586</v>
+        <v>-1.0191</v>
       </c>
       <c r="G18" t="n">
         <v>-2.0692</v>
@@ -1858,13 +1858,13 @@
         <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3448</v>
+        <v>0.2131</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7169</v>
+        <v>-0.2985</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3721</v>
+        <v>0.5115</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3581</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>O. OKENCHI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6524</v>
+        <v>-1.9447</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1442</v>
+        <v>-2.1991</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5082</v>
+        <v>0.2543</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.5045</v>
+        <v>-2.0938</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2255</v>
+        <v>-1.7678</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.279</v>
+        <v>-0.3261</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1242</v>
+        <v>-0.2975</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.308</v>
+        <v>-0.5737</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8161</v>
+        <v>0.2763</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3804</v>
+        <v>-1.7964</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9175</v>
+        <v>-1.194</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4629</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4107</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>2.0307</v>
+        <v>0.4785</v>
       </c>
       <c r="T19" t="n">
-        <v>2.0067</v>
+        <v>-0.0001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0241</v>
+        <v>0.4786</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5893</v>
+        <v>1.5187</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5893</v>
+        <v>0.3401</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. OKENCHI</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6623</v>
+        <v>-2.7263</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0945</v>
+        <v>-1.7132</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4322</v>
+        <v>-1.013</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0938</v>
+        <v>-3.5045</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7678</v>
+        <v>-2.2255</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3261</v>
+        <v>-1.279</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2975</v>
+        <v>-1.1242</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5737</v>
+        <v>-0.308</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2763</v>
+        <v>-0.8161</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7964</v>
+        <v>-2.3804</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.194</v>
+        <v>-1.9175</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.4629</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8481</v>
+        <v>0.4107</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7609</v>
+        <v>0.9569</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1045</v>
+        <v>0.4376</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6564</v>
+        <v>0.5192</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5187</v>
+        <v>-0.5893</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3401</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1528</v>
+        <v>-3.355</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6671</v>
+        <v>-2.7717</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4857</v>
+        <v>-0.5833</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0706</v>
@@ -2092,13 +2092,13 @@
         <v>2.6694</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4448</v>
+        <v>-0.647</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6201</v>
+        <v>-0.7247</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1753</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2267</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2905</v>
+        <v>-4.8216</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7702</v>
+        <v>-1.3517</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5204</v>
+        <v>-3.4698</v>
       </c>
       <c r="G22" t="n">
         <v>-5.1587</v>
@@ -2170,13 +2170,13 @@
         <v>2.6694</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2255</v>
+        <v>-0.7565</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.3916</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4155</v>
+        <v>-0.3649</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5758</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5925</v>
+        <v>-5.9352</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.4074</v>
+        <v>-5.7798</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.185</v>
+        <v>-0.1554</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9088</v>
@@ -2248,13 +2248,13 @@
         <v>1.4374</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8438</v>
+        <v>-1.1865</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9881</v>
+        <v>-0.3605</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8557</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1704</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.9701</v>
+        <v>-6.9571</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4783</v>
+        <v>-3.8507</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4917</v>
+        <v>-3.1064</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2789</v>
@@ -2326,13 +2326,13 @@
         <v>1.8481</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7733</v>
+        <v>-0.7604</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1857</v>
+        <v>-0.5581</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5876</v>
+        <v>-0.2023</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6591</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-24.338</v>
+        <v>-23.6408</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.9883</v>
+        <v>-12.9882</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.3497</v>
+        <v>-10.6523</v>
       </c>
       <c r="G25" t="n">
         <v>-16.7064</v>
@@ -2404,13 +2404,13 @@
         <v>18.4808</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.3977</v>
+        <v>-3.7001</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.8687</v>
+        <v>-2.8688</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.5289</v>
+        <v>-0.8316</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1539999999999999</v>
